--- a/Result/profitability/5469.xlsx
+++ b/Result/profitability/5469.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.59</v>
       </c>
       <c r="M2" t="n">
-        <v>1.37</v>
+        <v>1.2775</v>
       </c>
       <c r="N2" t="n">
-        <v>19.38875</v>
+        <v>18.06125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.47</v>
       </c>
       <c r="M3" t="n">
-        <v>1.23375</v>
+        <v>1.145</v>
       </c>
       <c r="N3" t="n">
-        <v>18.5575</v>
+        <v>17.84</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>1.12</v>
+        <v>1.0325</v>
       </c>
       <c r="N4" t="n">
-        <v>18.22125</v>
+        <v>17.54125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9237500000000001</v>
+        <v>0.8825</v>
       </c>
       <c r="N5" t="n">
-        <v>17.015</v>
+        <v>16.28125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.78875</v>
+        <v>0.60875</v>
       </c>
       <c r="N6" t="n">
-        <v>15.8125</v>
+        <v>15.19</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6325000000000001</v>
+        <v>0.595</v>
       </c>
       <c r="N7" t="n">
-        <v>15.93625</v>
+        <v>15.615</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.62375</v>
+        <v>0.5725</v>
       </c>
       <c r="N8" t="n">
-        <v>15.96875</v>
+        <v>15.82625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5837500000000001</v>
+        <v>0.58375</v>
       </c>
       <c r="N11" t="n">
         <v>15.54</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5469</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>16845</v>
+      </c>
+      <c r="D75" t="n">
+        <v>14308</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2537</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1155</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.86%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-117</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1038</v>
+      </c>
+      <c r="K75" t="n">
+        <v>397</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.39875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.605</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.139999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07037037037037031</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.2869565217391304</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.869999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2804586717630195</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
